--- a/data/00991A/20260427.xlsx
+++ b/data/00991A/20260427.xlsx
@@ -19,19 +19,19 @@
     <x:t>復華台灣未來50主動式ETF基金(基金之配息來源可能為收益平準金)（證劵代碼：00991A）</x:t>
   </x:si>
   <x:si>
-    <x:t>日期: 2026/04/24</x:t>
+    <x:t>日期: 2026/04/27</x:t>
   </x:si>
   <x:si>
     <x:t>基金資產淨值</x:t>
   </x:si>
   <x:si>
-    <x:t>33,662,750,937</x:t>
+    <x:t>36,308,146,335</x:t>
   </x:si>
   <x:si>
     <x:t>基金在外流通單位數</x:t>
   </x:si>
   <x:si>
-    <x:t>2,072,916,000</x:t>
+    <x:t>2,189,916,000</x:t>
   </x:si>
   <x:si>
     <x:t>基金每單位淨值</x:t>
@@ -58,13 +58,13 @@
     <x:t>台灣積體</x:t>
   </x:si>
   <x:si>
-    <x:t>2,300,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5,025,500,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.929%</x:t>
+    <x:t>3,550,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8,040,750,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.146%</x:t>
   </x:si>
   <x:si>
     <x:t>2383</x:t>
@@ -76,10 +76,10 @@
     <x:t>765,000</x:t>
   </x:si>
   <x:si>
-    <x:t>3,423,375,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.170%</x:t>
+    <x:t>3,618,450,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.966%</x:t>
   </x:si>
   <x:si>
     <x:t>3037</x:t>
@@ -91,10 +91,10 @@
     <x:t>3,200,000</x:t>
   </x:si>
   <x:si>
-    <x:t>2,528,000,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.510%</x:t>
+    <x:t>2,684,800,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.394%</x:t>
   </x:si>
   <x:si>
     <x:t>8299</x:t>
@@ -106,10 +106,10 @@
     <x:t>1,300,000</x:t>
   </x:si>
   <x:si>
-    <x:t>2,184,000,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6.488%</x:t>
+    <x:t>2,385,500,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.570%</x:t>
   </x:si>
   <x:si>
     <x:t>2308</x:t>
@@ -121,10 +121,10 @@
     <x:t>1,020,000</x:t>
   </x:si>
   <x:si>
-    <x:t>2,116,500,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6.287%</x:t>
+    <x:t>2,060,400,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.675%</x:t>
   </x:si>
   <x:si>
     <x:t>5274</x:t>
@@ -136,10 +136,10 @@
     <x:t>100,000</x:t>
   </x:si>
   <x:si>
-    <x:t>1,637,000,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.863%</x:t>
+    <x:t>1,600,000,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.407%</x:t>
   </x:si>
   <x:si>
     <x:t>3017</x:t>
@@ -151,10 +151,10 @@
     <x:t>550,000</x:t>
   </x:si>
   <x:si>
-    <x:t>1,619,750,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.812%</x:t>
+    <x:t>1,559,250,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.294%</x:t>
   </x:si>
   <x:si>
     <x:t>2345</x:t>
@@ -166,10 +166,10 @@
     <x:t>700,000</x:t>
   </x:si>
   <x:si>
-    <x:t>1,498,000,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.450%</x:t>
+    <x:t>1,522,500,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.193%</x:t>
   </x:si>
   <x:si>
     <x:t>8046</x:t>
@@ -181,10 +181,10 @@
     <x:t>1,650,000</x:t>
   </x:si>
   <x:si>
-    <x:t>1,442,100,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.284%</x:t>
+    <x:t>1,506,450,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.149%</x:t>
   </x:si>
   <x:si>
     <x:t>2368</x:t>
@@ -196,10 +196,10 @@
     <x:t>1,000,000</x:t>
   </x:si>
   <x:si>
-    <x:t>1,390,000,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.129%</x:t>
+    <x:t>1,420,000,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.911%</x:t>
   </x:si>
   <x:si>
     <x:t>2408</x:t>
@@ -211,10 +211,10 @@
     <x:t>6,200,000</x:t>
   </x:si>
   <x:si>
-    <x:t>1,277,200,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.794%</x:t>
+    <x:t>1,404,300,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.868%</x:t>
   </x:si>
   <x:si>
     <x:t>7769</x:t>
@@ -226,7 +226,25 @@
     <x:t>270,000</x:t>
   </x:si>
   <x:si>
-    <x:t>1,277,100,000</x:t>
+    <x:t>1,341,900,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.696%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6223</x:t>
+  </x:si>
+  <x:si>
+    <x:t>旺矽科技</x:t>
+  </x:si>
+  <x:si>
+    <x:t>260,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,268,800,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.495%</x:t>
   </x:si>
   <x:si>
     <x:t>2454</x:t>
@@ -241,22 +259,22 @@
     <x:t>1,217,500,000</x:t>
   </x:si>
   <x:si>
-    <x:t>3.617%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6223</x:t>
-  </x:si>
-  <x:si>
-    <x:t>旺矽科技</x:t>
-  </x:si>
-  <x:si>
-    <x:t>260,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,209,000,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.592%</x:t>
+    <x:t>3.353%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>景碩科技</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,000,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,030,000,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.837%</x:t>
   </x:si>
   <x:si>
     <x:t>3653</x:t>
@@ -268,25 +286,10 @@
     <x:t>200,000</x:t>
   </x:si>
   <x:si>
-    <x:t>1,074,000,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.190%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>景碩科技</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2,000,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,052,000,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.125%</x:t>
+    <x:t>992,000,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.732%</x:t>
   </x:si>
   <x:si>
     <x:t>3665</x:t>
@@ -298,10 +301,169 @@
     <x:t>370,000</x:t>
   </x:si>
   <x:si>
-    <x:t>1,023,050,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.039%</x:t>
+    <x:t>973,100,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.680%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2327</x:t>
+  </x:si>
+  <x:si>
+    <x:t>國巨股份</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,100,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>335,500,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.924%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1590</x:t>
+  </x:si>
+  <x:si>
+    <x:t>亞德客-KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>235,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>331,350,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.913%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>漢唐集成</x:t>
+  </x:si>
+  <x:si>
+    <x:t>330,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>319,770,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.881%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>聯亞光電</x:t>
+  </x:si>
+  <x:si>
+    <x:t>110,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>279,400,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.770%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6515</x:t>
+  </x:si>
+  <x:si>
+    <x:t>穎崴科技</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9,580,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.026%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3711</x:t>
+  </x:si>
+  <x:si>
+    <x:t>日月光投</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,459,500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.012%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2059</x:t>
+  </x:si>
+  <x:si>
+    <x:t>川湖科技</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,960,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.011%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6510</x:t>
+  </x:si>
+  <x:si>
+    <x:t>中華精測</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,570,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.010%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2382</x:t>
+  </x:si>
+  <x:si>
+    <x:t>廣達電腦</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,929,500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.008%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2449</x:t>
+  </x:si>
+  <x:si>
+    <x:t>京元電子</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,551,500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.007%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>華通電腦</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,119,500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.006%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2317</x:t>
+  </x:si>
+  <x:si>
+    <x:t>鴻海精密</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,052,000</x:t>
   </x:si>
   <x:si>
     <x:t>2360</x:t>
@@ -310,169 +472,10 @@
     <x:t>致茂電子</x:t>
   </x:si>
   <x:si>
-    <x:t>460,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>883,200,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.624%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2327</x:t>
-  </x:si>
-  <x:si>
-    <x:t>國巨股份</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,100,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>326,700,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.971%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2404</x:t>
-  </x:si>
-  <x:si>
-    <x:t>漢唐集成</x:t>
-  </x:si>
-  <x:si>
-    <x:t>330,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>326,370,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.970%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1590</x:t>
-  </x:si>
-  <x:si>
-    <x:t>亞德客-KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>235,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>319,600,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.949%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>聯亞光電</x:t>
-  </x:si>
-  <x:si>
-    <x:t>110,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>310,200,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.921%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6515</x:t>
-  </x:si>
-  <x:si>
-    <x:t>穎崴科技</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,060,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.030%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3711</x:t>
-  </x:si>
-  <x:si>
-    <x:t>日月光投</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4,464,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.013%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2059</x:t>
-  </x:si>
-  <x:si>
-    <x:t>川湖科技</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3,795,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.011%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6510</x:t>
-  </x:si>
-  <x:si>
-    <x:t>中華精測</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3,630,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2382</x:t>
-  </x:si>
-  <x:si>
-    <x:t>廣達電腦</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2,907,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.009%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2449</x:t>
-  </x:si>
-  <x:si>
-    <x:t>京元電子</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2,574,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.008%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2317</x:t>
-  </x:si>
-  <x:si>
-    <x:t>鴻海精密</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,993,500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.006%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2313</x:t>
-  </x:si>
-  <x:si>
-    <x:t>華通電腦</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,930,500</x:t>
+    <x:t>1,925,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.005%</x:t>
   </x:si>
   <x:si>
     <x:t>2603</x:t>
@@ -481,10 +484,7 @@
     <x:t>長榮海運</x:t>
   </x:si>
   <x:si>
-    <x:t>1,813,500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.005%</x:t>
+    <x:t>1,795,500</x:t>
   </x:si>
   <x:si>
     <x:t>3231</x:t>
@@ -493,19 +493,31 @@
     <x:t>緯創資通</x:t>
   </x:si>
   <x:si>
-    <x:t>1,273,500</x:t>
+    <x:t>1,282,500</x:t>
   </x:si>
   <x:si>
     <x:t>0.004%</x:t>
   </x:si>
   <x:si>
+    <x:t>2337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>旺宏電子</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,305,000</x:t>
+  </x:si>
+  <x:si>
     <x:t>5347</x:t>
   </x:si>
   <x:si>
     <x:t>世界先進</x:t>
   </x:si>
   <x:si>
-    <x:t>1,264,500</x:t>
+    <x:t>1,246,500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.003%</x:t>
   </x:si>
   <x:si>
     <x:t>8210</x:t>
@@ -514,16 +526,7 @@
     <x:t>勤誠興業</x:t>
   </x:si>
   <x:si>
-    <x:t>1,210,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>旺宏電子</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,188,000</x:t>
+    <x:t>1,165,000</x:t>
   </x:si>
   <x:si>
     <x:t>6274</x:t>
@@ -532,10 +535,7 @@
     <x:t>台燿科技</x:t>
   </x:si>
   <x:si>
-    <x:t>1,045,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.003%</x:t>
+    <x:t>990,000</x:t>
   </x:si>
   <x:si>
     <x:t>1519</x:t>
@@ -544,7 +544,10 @@
     <x:t>華城電機</x:t>
   </x:si>
   <x:si>
-    <x:t>886,000</x:t>
+    <x:t>888,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.002%</x:t>
   </x:si>
   <x:si>
     <x:t>2344</x:t>
@@ -553,10 +556,7 @@
     <x:t>華邦電子</x:t>
   </x:si>
   <x:si>
-    <x:t>793,800</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.002%</x:t>
+    <x:t>845,100</x:t>
   </x:si>
   <x:si>
     <x:t>2881</x:t>
@@ -565,7 +565,7 @@
     <x:t>富邦金融</x:t>
   </x:si>
   <x:si>
-    <x:t>790,200</x:t>
+    <x:t>791,100</x:t>
   </x:si>
   <x:si>
     <x:t>2882</x:t>
@@ -574,7 +574,7 @@
     <x:t>國泰金融</x:t>
   </x:si>
   <x:si>
-    <x:t>674,100</x:t>
+    <x:t>670,500</x:t>
   </x:si>
   <x:si>
     <x:t>3044</x:t>
@@ -583,7 +583,7 @@
     <x:t>健鼎科技</x:t>
   </x:si>
   <x:si>
-    <x:t>480,500</x:t>
+    <x:t>485,000</x:t>
   </x:si>
   <x:si>
     <x:t>0.001%</x:t>
@@ -595,7 +595,7 @@
     <x:t>中國信託</x:t>
   </x:si>
   <x:si>
-    <x:t>476,100</x:t>
+    <x:t>474,300</x:t>
   </x:si>
   <x:si>
     <x:t>2885</x:t>
@@ -604,7 +604,7 @@
     <x:t>元大金融</x:t>
   </x:si>
   <x:si>
-    <x:t>449,550</x:t>
+    <x:t>457,200</x:t>
   </x:si>
   <x:si>
     <x:t>2890</x:t>
@@ -613,7 +613,7 @@
     <x:t>永豐金融</x:t>
   </x:si>
   <x:si>
-    <x:t>287,550</x:t>
+    <x:t>285,750</x:t>
   </x:si>
   <x:si>
     <x:t>3036</x:t>
@@ -622,7 +622,19 @@
     <x:t>文曄科技</x:t>
   </x:si>
   <x:si>
-    <x:t>199,000</x:t>
+    <x:t>201,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3045</x:t>
+  </x:si>
+  <x:si>
+    <x:t>台灣大哥</x:t>
+  </x:si>
+  <x:si>
+    <x:t>112,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.000%</x:t>
   </x:si>
   <x:si>
     <x:t>2412</x:t>
@@ -631,19 +643,7 @@
     <x:t>中華電信</x:t>
   </x:si>
   <x:si>
-    <x:t>135,500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.000%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3045</x:t>
-  </x:si>
-  <x:si>
-    <x:t>台灣大哥</x:t>
-  </x:si>
-  <x:si>
-    <x:t>113,000</x:t>
+    <x:t>137,000</x:t>
   </x:si>
   <x:si>
     <x:t>5871</x:t>
@@ -652,7 +652,7 @@
     <x:t>中租-KY</x:t>
   </x:si>
   <x:si>
-    <x:t>121,500</x:t>
+    <x:t>116,000</x:t>
   </x:si>
   <x:si>
     <x:t>1303</x:t>
@@ -661,7 +661,7 @@
     <x:t>南亞塑膠</x:t>
   </x:si>
   <x:si>
-    <x:t>85,900</x:t>
+    <x:t>87,800</x:t>
   </x:si>
   <x:si>
     <x:t>6505</x:t>
@@ -670,7 +670,7 @@
     <x:t>台塑石化</x:t>
   </x:si>
   <x:si>
-    <x:t>51,600</x:t>
+    <x:t>51,800</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1127,7 +1127,7 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="3" t="n">
-        <x:v>16.24</x:v>
+        <x:v>16.58</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
@@ -1348,205 +1348,205 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="E23" s="6" t="s">
-        <x:v>66</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B24" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C24" s="6" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D24" s="6" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E24" s="6" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="5" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B25" s="4" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C25" s="6" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D25" s="6" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E25" s="6" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="5" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B26" s="4" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C26" s="6" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D26" s="6" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E26" s="6" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="5" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B27" s="4" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C27" s="6" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D27" s="6" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E27" s="6" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="5" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B28" s="4" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C28" s="6" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D28" s="6" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E28" s="6" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="5" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B29" s="4" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C29" s="6" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D29" s="6" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E29" s="6" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="5" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B30" s="4" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C30" s="6" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D30" s="6" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E30" s="6" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="5" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B31" s="4" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C31" s="6" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D31" s="6" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E31" s="6" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="5" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B32" s="4" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C32" s="6" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D32" s="6" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E32" s="6" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="5" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B33" s="4" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C33" s="6" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D33" s="6" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E33" s="6" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="5" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B34" s="4" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C34" s="6" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D34" s="6" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E34" s="6" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="5" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B35" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C35" s="6" t="s">
-        <x:v>128</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D35" s="6" t="s">
         <x:v>129</x:v>
@@ -1563,7 +1563,7 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="C36" s="6" t="s">
-        <x:v>123</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D36" s="6" t="s">
         <x:v>133</x:v>
@@ -1580,64 +1580,64 @@
         <x:v>136</x:v>
       </x:c>
       <x:c r="C37" s="6" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D37" s="6" t="s">
         <x:v>137</x:v>
       </x:c>
       <x:c r="E37" s="6" t="s">
-        <x:v>134</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="5" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B38" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C38" s="6" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D38" s="6" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E38" s="6" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="5" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B39" s="4" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C39" s="6" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D39" s="6" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E39" s="6" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="5" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B40" s="4" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="C40" s="6" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D40" s="6" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="E40" s="6" t="s">
         <x:v>146</x:v>
-      </x:c>
-      <x:c r="B40" s="4" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="C40" s="6" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D40" s="6" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="E40" s="6" t="s">
-        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
@@ -1648,30 +1648,30 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="C41" s="6" t="s">
-        <x:v>128</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D41" s="6" t="s">
         <x:v>152</x:v>
       </x:c>
       <x:c r="E41" s="6" t="s">
-        <x:v>149</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="5" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="B42" s="4" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="C42" s="6" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D42" s="6" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="E42" s="6" t="s">
         <x:v>153</x:v>
-      </x:c>
-      <x:c r="B42" s="4" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="C42" s="6" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D42" s="6" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="E42" s="6" t="s">
-        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5">
@@ -1682,7 +1682,7 @@
         <x:v>158</x:v>
       </x:c>
       <x:c r="C43" s="6" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D43" s="6" t="s">
         <x:v>159</x:v>
@@ -1699,7 +1699,7 @@
         <x:v>162</x:v>
       </x:c>
       <x:c r="C44" s="6" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D44" s="6" t="s">
         <x:v>163</x:v>
@@ -1716,47 +1716,47 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="C45" s="6" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D45" s="6" t="s">
         <x:v>166</x:v>
       </x:c>
       <x:c r="E45" s="6" t="s">
-        <x:v>160</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="B46" s="4" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C46" s="6" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D46" s="6" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="E46" s="6" t="s">
         <x:v>167</x:v>
-      </x:c>
-      <x:c r="B46" s="4" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="C46" s="6" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D46" s="6" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="E46" s="6" t="s">
-        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="5" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B47" s="4" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C47" s="6" t="s">
-        <x:v>123</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D47" s="6" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E47" s="6" t="s">
-        <x:v>173</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5">
@@ -1767,30 +1767,30 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="C48" s="6" t="s">
-        <x:v>123</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D48" s="6" t="s">
         <x:v>176</x:v>
       </x:c>
       <x:c r="E48" s="6" t="s">
-        <x:v>173</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="5" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="B49" s="4" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="C49" s="6" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D49" s="6" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="E49" s="6" t="s">
         <x:v>177</x:v>
-      </x:c>
-      <x:c r="B49" s="4" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="C49" s="6" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D49" s="6" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="E49" s="6" t="s">
-        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5">
@@ -1801,13 +1801,13 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="C50" s="6" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D50" s="6" t="s">
         <x:v>183</x:v>
       </x:c>
       <x:c r="E50" s="6" t="s">
-        <x:v>180</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
@@ -1818,13 +1818,13 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="C51" s="6" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D51" s="6" t="s">
         <x:v>186</x:v>
       </x:c>
       <x:c r="E51" s="6" t="s">
-        <x:v>180</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5">
@@ -1835,7 +1835,7 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="C52" s="6" t="s">
-        <x:v>123</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D52" s="6" t="s">
         <x:v>189</x:v>
@@ -1852,7 +1852,7 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="C53" s="6" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D53" s="6" t="s">
         <x:v>193</x:v>
@@ -1869,7 +1869,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="C54" s="6" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D54" s="6" t="s">
         <x:v>196</x:v>
@@ -1886,7 +1886,7 @@
         <x:v>198</x:v>
       </x:c>
       <x:c r="C55" s="6" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D55" s="6" t="s">
         <x:v>199</x:v>
@@ -1903,7 +1903,7 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="C56" s="6" t="s">
-        <x:v>123</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D56" s="6" t="s">
         <x:v>202</x:v>
@@ -1920,7 +1920,7 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="C57" s="6" t="s">
-        <x:v>123</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D57" s="6" t="s">
         <x:v>205</x:v>
@@ -1937,7 +1937,7 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="C58" s="6" t="s">
-        <x:v>123</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D58" s="6" t="s">
         <x:v>209</x:v>
@@ -1954,7 +1954,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="C59" s="6" t="s">
-        <x:v>123</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D59" s="6" t="s">
         <x:v>212</x:v>
@@ -1971,7 +1971,7 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="C60" s="6" t="s">
-        <x:v>123</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D60" s="6" t="s">
         <x:v>215</x:v>
@@ -1988,7 +1988,7 @@
         <x:v>217</x:v>
       </x:c>
       <x:c r="C61" s="6" t="s">
-        <x:v>123</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D61" s="6" t="s">
         <x:v>218</x:v>
